--- a/AAAGameData/DataTables/TreasureBoxTable.xlsx
+++ b/AAAGameData/DataTables/TreasureBoxTable.xlsx
@@ -1210,10 +1210,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H5" s="2">
         <v>1</v>

--- a/AAAGameData/DataTables/TreasureBoxTable.xlsx
+++ b/AAAGameData/DataTables/TreasureBoxTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
   <si>
     <t>#</t>
   </si>
@@ -50,7 +50,25 @@
     <t>ItemCountMax</t>
   </si>
   <si>
-    <t>ItemGroupId</t>
+    <t>ItemGroupIds</t>
+  </si>
+  <si>
+    <t>CoinsProbability</t>
+  </si>
+  <si>
+    <t>MinCoins</t>
+  </si>
+  <si>
+    <t>MaxCoins</t>
+  </si>
+  <si>
+    <t>MagicaStoneProbability</t>
+  </si>
+  <si>
+    <t>MinMagicaStone</t>
+  </si>
+  <si>
+    <t>MaxMagicaStone</t>
   </si>
   <si>
     <t>Description</t>
@@ -62,6 +80,12 @@
     <t>string</t>
   </si>
   <si>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
     <t>宝箱ID</t>
   </si>
   <si>
@@ -80,7 +104,25 @@
     <t>开箱最大物品数</t>
   </si>
   <si>
-    <t>物品组ID</t>
+    <t>物品组ID列表</t>
+  </si>
+  <si>
+    <t>有金币的概率</t>
+  </si>
+  <si>
+    <t>最小金币数量</t>
+  </si>
+  <si>
+    <t>最大金币数量</t>
+  </si>
+  <si>
+    <t>有灵石的概率</t>
+  </si>
+  <si>
+    <t>最小灵石数量</t>
+  </si>
+  <si>
+    <t>最大灵石数量</t>
   </si>
   <si>
     <t>宝箱描述</t>
@@ -89,22 +131,34 @@
     <t>可疑的箱子</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>一个看起来很可疑的箱子</t>
   </si>
   <si>
+    <t>精致的宝箱</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>华丽的宝箱，散发着神秘光芒</t>
+  </si>
+  <si>
     <t>华丽的宝箱</t>
   </si>
   <si>
-    <t>华丽的宝箱，散发着神秘光芒</t>
-  </si>
-  <si>
-    <t>史诗珍宝库</t>
+    <t>3</t>
   </si>
   <si>
     <t>满是珍宝的宝箱</t>
   </si>
   <si>
     <t>神秘古董箱</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>传说中的古董宝藏</t>
@@ -728,17 +782,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1086,276 +1136,353 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:O8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="8" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="16.7777777777778" customWidth="1"/>
+    <col min="10" max="10" width="13.2222222222222" customWidth="1"/>
+    <col min="11" max="11" width="13.3333333333333" customWidth="1"/>
+    <col min="12" max="12" width="22.7777777777778" customWidth="1"/>
+    <col min="13" max="14" width="14.7777777777778" customWidth="1"/>
+    <col min="15" max="15" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:15">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:15">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:15">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:15">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1">
+        <v>8</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1">
+        <v>200</v>
+      </c>
+      <c r="K5" s="1">
+        <v>500</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="M5" s="1">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1">
+        <v>2</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:15">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>3</v>
+      </c>
+      <c r="G6" s="1">
+        <v>6</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="J6" s="1">
+        <v>500</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:15">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1">
+        <v>5</v>
+      </c>
+      <c r="G7" s="1">
+        <v>8</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1000</v>
+      </c>
+      <c r="K7" s="1">
+        <v>10000</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>4</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:15">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="1">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1">
+        <v>6</v>
+      </c>
+      <c r="G8" s="1">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:9">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2">
+      <c r="H8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>3</v>
-      </c>
-      <c r="G5" s="2">
-        <v>8</v>
-      </c>
-      <c r="H5" s="2">
+      <c r="J8" s="1">
+        <v>10000</v>
+      </c>
+      <c r="K8" s="1">
+        <v>100000</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="M8" s="1">
         <v>1</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" spans="1:9">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2">
-        <v>2</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2">
-        <v>3</v>
-      </c>
-      <c r="G6" s="2">
-        <v>6</v>
-      </c>
-      <c r="H6" s="2">
-        <v>2</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:9">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2">
-        <v>3</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="2">
-        <v>2</v>
-      </c>
-      <c r="F7" s="2">
+      <c r="N8" s="1">
         <v>5</v>
       </c>
-      <c r="G7" s="2">
-        <v>8</v>
-      </c>
-      <c r="H7" s="2">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:9">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2">
-        <v>4</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="2">
-        <v>3</v>
-      </c>
-      <c r="F8" s="2">
-        <v>6</v>
-      </c>
-      <c r="G8" s="2">
-        <v>10</v>
-      </c>
-      <c r="H8" s="2">
-        <v>4</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="C9" s="4"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="C10" s="4"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="C11" s="4"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="C12" s="4"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="C13" s="4"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="C14" s="4"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="C15" s="4"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="C16" s="4"/>
-    </row>
-    <row r="17" spans="3:3">
-      <c r="C17" s="4"/>
-    </row>
-    <row r="18" spans="3:3">
-      <c r="C18" s="4"/>
-    </row>
-    <row r="19" spans="3:3">
-      <c r="C19" s="4"/>
-    </row>
-    <row r="20" spans="3:3">
-      <c r="C20" s="4"/>
-    </row>
-    <row r="21" spans="3:3">
-      <c r="C21" s="4"/>
-    </row>
-    <row r="22" spans="3:3">
-      <c r="C22" s="4"/>
-    </row>
-    <row r="23" spans="3:3">
-      <c r="C23" s="4"/>
-    </row>
-    <row r="24" spans="3:3">
-      <c r="C24" s="4"/>
-    </row>
-    <row r="25" spans="3:3">
-      <c r="C25" s="4"/>
-    </row>
-    <row r="26" spans="3:3">
-      <c r="C26" s="4"/>
-    </row>
-    <row r="27" spans="3:3">
-      <c r="C27" s="4"/>
-    </row>
-    <row r="28" spans="3:3">
-      <c r="C28" s="4"/>
+      <c r="O8" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AAAGameData/DataTables/TreasureBoxTable.xlsx
+++ b/AAAGameData/DataTables/TreasureBoxTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
     <t>宝箱描述</t>
   </si>
   <si>
-    <t>可疑的箱子</t>
+    <t>破损的宝箱</t>
   </si>
   <si>
     <t>1</t>
@@ -155,7 +155,7 @@
     <t>满是珍宝的宝箱</t>
   </si>
   <si>
-    <t>神秘古董箱</t>
+    <t>神秘的宝箱</t>
   </si>
   <si>
     <t>4</t>
@@ -174,14 +174,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -637,148 +630,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1137,7 +1130,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1146,11 +1139,11 @@
     <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="16.7777777777778" customWidth="1"/>
-    <col min="10" max="10" width="13.2222222222222" customWidth="1"/>
+    <col min="9" max="9" width="16.775" customWidth="1"/>
+    <col min="10" max="10" width="13.225" customWidth="1"/>
     <col min="11" max="11" width="13.3333333333333" customWidth="1"/>
-    <col min="12" max="12" width="22.7777777777778" customWidth="1"/>
-    <col min="13" max="14" width="14.7777777777778" customWidth="1"/>
+    <col min="12" max="12" width="22.775" customWidth="1"/>
+    <col min="13" max="14" width="14.775" customWidth="1"/>
     <col min="15" max="15" width="28" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1334,7 +1327,7 @@
         <v>34</v>
       </c>
       <c r="I5" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J5" s="1">
         <v>200</v>
@@ -1346,7 +1339,7 @@
         <v>0.2</v>
       </c>
       <c r="M5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" s="1">
         <v>2</v>

--- a/AAAGameData/DataTables/TreasureBoxTable.xlsx
+++ b/AAAGameData/DataTables/TreasureBoxTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
   <si>
     <t>#</t>
   </si>
@@ -41,6 +41,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>PrefabId</t>
+  </si>
+  <si>
     <t>Rarity</t>
   </si>
   <si>
@@ -93,6 +96,9 @@
   </si>
   <si>
     <t>宝箱名字</t>
+  </si>
+  <si>
+    <t>预制体资源Id</t>
   </si>
   <si>
     <t>稀有度(0普通 1稀有 2史诗 3传说)</t>
@@ -1129,25 +1135,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="33" customWidth="1"/>
-    <col min="6" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="16.775" customWidth="1"/>
-    <col min="10" max="10" width="13.225" customWidth="1"/>
-    <col min="11" max="11" width="13.3333333333333" customWidth="1"/>
-    <col min="12" max="12" width="22.775" customWidth="1"/>
-    <col min="13" max="14" width="14.775" customWidth="1"/>
-    <col min="15" max="15" width="28" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="33" customWidth="1"/>
+    <col min="7" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="16.775" customWidth="1"/>
+    <col min="11" max="11" width="13.225" customWidth="1"/>
+    <col min="12" max="12" width="13.3333333333333" customWidth="1"/>
+    <col min="13" max="13" width="22.775" customWidth="1"/>
+    <col min="14" max="15" width="14.775" customWidth="1"/>
+    <col min="16" max="16" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1159,16 +1166,17 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="2"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1188,10 +1196,10 @@
       <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J2" s="1" t="s">
@@ -1212,269 +1220,290 @@
       <c r="O2" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="P2" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="P3" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" ht="27" spans="1:16">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="I4" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="J4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:15">
+    <row r="5" ht="15" customHeight="1" spans="1:16">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" s="1">
+        <v>2501</v>
+      </c>
+      <c r="F5" s="1">
         <v>0</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>3</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>8</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="1">
+      <c r="I5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="1">
         <v>0.5</v>
       </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
         <v>200</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>500</v>
       </c>
-      <c r="L5" s="1">
+      <c r="M5" s="1">
         <v>0.2</v>
       </c>
-      <c r="M5" s="1">
+      <c r="N5" s="1">
         <v>0</v>
       </c>
-      <c r="N5" s="1">
+      <c r="O5" s="1">
         <v>2</v>
       </c>
-      <c r="O5" s="1" t="s">
-        <v>35</v>
+      <c r="P5" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:15">
+    <row r="6" ht="15" customHeight="1" spans="1:16">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E6" s="1">
+        <v>2502</v>
+      </c>
+      <c r="F6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>3</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>6</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="1">
+      <c r="I6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="1">
         <v>0.6</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>500</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>1000</v>
       </c>
-      <c r="L6" s="1">
+      <c r="M6" s="1">
         <v>0.4</v>
       </c>
-      <c r="M6" s="1">
+      <c r="N6" s="1">
         <v>0</v>
       </c>
-      <c r="N6" s="1">
+      <c r="O6" s="1">
         <v>3</v>
       </c>
-      <c r="O6" s="1" t="s">
-        <v>38</v>
+      <c r="P6" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:15">
+    <row r="7" ht="15" customHeight="1" spans="1:16">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E7" s="1">
+        <v>2503</v>
+      </c>
+      <c r="F7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>5</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>8</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="1">
+      <c r="I7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="1">
         <v>0.8</v>
       </c>
-      <c r="J7" s="1">
+      <c r="K7" s="1">
         <v>1000</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>10000</v>
       </c>
-      <c r="L7" s="1">
+      <c r="M7" s="1">
         <v>0.6</v>
       </c>
-      <c r="M7" s="1">
+      <c r="N7" s="1">
         <v>0</v>
       </c>
-      <c r="N7" s="1">
+      <c r="O7" s="1">
         <v>4</v>
       </c>
-      <c r="O7" s="1" t="s">
-        <v>41</v>
+      <c r="P7" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:15">
+    <row r="8" ht="15" customHeight="1" spans="1:16">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E8" s="1">
+        <v>2504</v>
+      </c>
+      <c r="F8" s="1">
         <v>3</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>6</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>10</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="1">
+      <c r="I8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" s="1">
         <v>1</v>
       </c>
-      <c r="J8" s="1">
+      <c r="K8" s="1">
         <v>10000</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>100000</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <v>0.8</v>
       </c>
-      <c r="M8" s="1">
+      <c r="N8" s="1">
         <v>1</v>
       </c>
-      <c r="N8" s="1">
+      <c r="O8" s="1">
         <v>5</v>
       </c>
-      <c r="O8" s="1" t="s">
-        <v>44</v>
+      <c r="P8" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/TreasureBoxTable.xlsx
+++ b/AAAGameData/DataTables/TreasureBoxTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
   <si>
     <t>#</t>
   </si>
@@ -83,9 +83,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>int[]</t>
-  </si>
-  <si>
     <t>double</t>
   </si>
   <si>
@@ -110,7 +107,7 @@
     <t>开箱最大物品数</t>
   </si>
   <si>
-    <t>物品组ID列表</t>
+    <t>物品组ID权重(JSON格式:ID1:权重1,ID2:权重2...)</t>
   </si>
   <si>
     <t>有金币的概率</t>
@@ -137,7 +134,7 @@
     <t>破损的宝箱</t>
   </si>
   <si>
-    <t>1</t>
+    <t>1:10</t>
   </si>
   <si>
     <t>一个看起来很可疑的箱子</t>
@@ -146,28 +143,40 @@
     <t>精致的宝箱</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>华丽的宝箱，散发着神秘光芒</t>
   </si>
   <si>
     <t>华丽的宝箱</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>满是珍宝的宝箱</t>
   </si>
   <si>
     <t>神秘的宝箱</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>传说中的古董宝藏</t>
+  </si>
+  <si>
+    <t>普通敌人奖励</t>
+  </si>
+  <si>
+    <t>普通敌人战斗奖励</t>
+  </si>
+  <si>
+    <t>精英敌人奖励</t>
+  </si>
+  <si>
+    <t>精英敌人战斗奖励</t>
+  </si>
+  <si>
+    <t>Boss奖励</t>
+  </si>
+  <si>
+    <t>1:10,9:-1</t>
+  </si>
+  <si>
+    <t>Boss战斗奖励</t>
   </si>
 </sst>
 </file>
@@ -180,7 +189,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -636,157 +652,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1135,22 +1148,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <dimension ref="A1:P11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="4" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="33" customWidth="1"/>
     <col min="7" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="16.775" customWidth="1"/>
-    <col min="11" max="11" width="13.225" customWidth="1"/>
-    <col min="12" max="12" width="13.3333333333333" customWidth="1"/>
-    <col min="13" max="13" width="22.775" customWidth="1"/>
-    <col min="14" max="15" width="14.775" customWidth="1"/>
+    <col min="9" max="9" width="47" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="24" customWidth="1"/>
+    <col min="14" max="15" width="16" customWidth="1"/>
     <col min="16" max="16" width="28" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1167,7 +1178,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="2"/>
+      <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -1199,7 +1210,7 @@
       <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J2" s="1" t="s">
@@ -1247,11 +1258,11 @@
       <c r="H3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>16</v>
@@ -1260,7 +1271,7 @@
         <v>16</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>16</v>
@@ -1272,54 +1283,54 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:16">
+    <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:16">
@@ -1329,7 +1340,7 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1">
         <v>2501</v>
@@ -1343,8 +1354,8 @@
       <c r="H5" s="1">
         <v>8</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>36</v>
+      <c r="I5" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="J5" s="1">
         <v>0.5</v>
@@ -1365,7 +1376,7 @@
         <v>2</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:16">
@@ -1375,7 +1386,7 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1">
         <v>2502</v>
@@ -1389,8 +1400,8 @@
       <c r="H6" s="1">
         <v>6</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>39</v>
+      <c r="I6" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="J6" s="1">
         <v>0.6</v>
@@ -1411,7 +1422,7 @@
         <v>3</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:16">
@@ -1421,7 +1432,7 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E7" s="1">
         <v>2503</v>
@@ -1435,8 +1446,8 @@
       <c r="H7" s="1">
         <v>8</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>42</v>
+      <c r="I7" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="J7" s="1">
         <v>0.8</v>
@@ -1457,7 +1468,7 @@
         <v>4</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:16">
@@ -1467,7 +1478,7 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E8" s="1">
         <v>2504</v>
@@ -1481,8 +1492,8 @@
       <c r="H8" s="1">
         <v>10</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>45</v>
+      <c r="I8" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="J8" s="1">
         <v>1</v>
@@ -1503,7 +1514,145 @@
         <v>5</v>
       </c>
       <c r="P8" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:16">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1">
+        <v>101</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1">
+        <v>3</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="K9" s="1">
+        <v>50</v>
+      </c>
+      <c r="L9" s="1">
+        <v>200</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1">
+        <v>1</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:16">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1">
+        <v>102</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>2</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2</v>
+      </c>
+      <c r="H10" s="1">
+        <v>5</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1">
+        <v>200</v>
+      </c>
+      <c r="L10" s="1">
+        <v>500</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>2</v>
+      </c>
+      <c r="P10" s="1" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:16">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1">
+        <v>103</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1">
+        <v>3</v>
+      </c>
+      <c r="H11" s="1">
+        <v>8</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="K11" s="1">
+        <v>500</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1500</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="N11" s="1">
+        <v>1</v>
+      </c>
+      <c r="O11" s="1">
+        <v>3</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/TreasureBoxTable.xlsx
+++ b/AAAGameData/DataTables/TreasureBoxTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="48">
   <si>
     <t>#</t>
   </si>
@@ -44,9 +44,6 @@
     <t>PrefabId</t>
   </si>
   <si>
-    <t>Rarity</t>
-  </si>
-  <si>
     <t>ItemCountMin</t>
   </si>
   <si>
@@ -96,9 +93,6 @@
   </si>
   <si>
     <t>预制体资源Id</t>
-  </si>
-  <si>
-    <t>稀有度(0普通 1稀有 2史诗 3传说)</t>
   </si>
   <si>
     <t>开箱最小物品数</t>
@@ -1148,24 +1142,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="33" customWidth="1"/>
-    <col min="7" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="47" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="24" customWidth="1"/>
-    <col min="14" max="15" width="16" customWidth="1"/>
-    <col min="16" max="16" width="28" customWidth="1"/>
+    <col min="6" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="47" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="13" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1185,9 +1178,8 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1231,29 +1223,26 @@
       <c r="O2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>16</v>
@@ -1262,269 +1251,251 @@
         <v>17</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="1" t="s">
-        <v>17</v>
-      </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>33</v>
-      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:16">
+    <row r="5" ht="15" customHeight="1" spans="1:15">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E5" s="1">
         <v>2501</v>
       </c>
       <c r="F5" s="1">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1">
+        <v>8</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="J5" s="1">
+        <v>200</v>
+      </c>
+      <c r="K5" s="1">
+        <v>500</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="M5" s="1">
         <v>0</v>
       </c>
-      <c r="G5" s="1">
-        <v>3</v>
-      </c>
-      <c r="H5" s="1">
-        <v>8</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="K5" s="1">
-        <v>200</v>
-      </c>
-      <c r="L5" s="1">
-        <v>500</v>
-      </c>
-      <c r="M5" s="1">
-        <v>0.2</v>
-      </c>
       <c r="N5" s="1">
-        <v>0</v>
-      </c>
-      <c r="O5" s="1">
         <v>2</v>
       </c>
-      <c r="P5" s="1" t="s">
-        <v>36</v>
+      <c r="O5" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:16">
+    <row r="6" ht="15" customHeight="1" spans="1:15">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E6" s="1">
         <v>2502</v>
       </c>
       <c r="F6" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
+        <v>6</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="J6" s="1">
+        <v>500</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
         <v>3</v>
       </c>
-      <c r="H6" s="1">
-        <v>6</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="K6" s="1">
-        <v>500</v>
-      </c>
-      <c r="L6" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M6" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="N6" s="1">
-        <v>0</v>
-      </c>
-      <c r="O6" s="1">
-        <v>3</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>38</v>
+      <c r="O6" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:16">
+    <row r="7" ht="15" customHeight="1" spans="1:15">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E7" s="1">
         <v>2503</v>
       </c>
       <c r="F7" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>5</v>
-      </c>
-      <c r="H7" s="1">
         <v>8</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>35</v>
+      <c r="H7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.8</v>
       </c>
       <c r="J7" s="1">
-        <v>0.8</v>
+        <v>1000</v>
       </c>
       <c r="K7" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="L7" s="1">
-        <v>10000</v>
+        <v>0.6</v>
       </c>
       <c r="M7" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N7" s="1">
-        <v>0</v>
-      </c>
-      <c r="O7" s="1">
         <v>4</v>
       </c>
-      <c r="P7" s="1" t="s">
-        <v>40</v>
+      <c r="O7" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:16">
+    <row r="8" ht="15" customHeight="1" spans="1:15">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E8" s="1">
         <v>2504</v>
       </c>
       <c r="F8" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>6</v>
-      </c>
-      <c r="H8" s="1">
         <v>10</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>35</v>
+      <c r="H8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1</v>
       </c>
       <c r="J8" s="1">
+        <v>10000</v>
+      </c>
+      <c r="K8" s="1">
+        <v>100000</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="M8" s="1">
         <v>1</v>
       </c>
-      <c r="K8" s="1">
-        <v>10000</v>
-      </c>
-      <c r="L8" s="1">
-        <v>100000</v>
-      </c>
-      <c r="M8" s="1">
-        <v>0.8</v>
-      </c>
       <c r="N8" s="1">
-        <v>1</v>
-      </c>
-      <c r="O8" s="1">
         <v>5</v>
       </c>
-      <c r="P8" s="1" t="s">
-        <v>42</v>
+      <c r="O8" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:16">
+    <row r="9" ht="15" customHeight="1" spans="1:15">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>101</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -1533,44 +1504,41 @@
         <v>1</v>
       </c>
       <c r="G9" s="1">
+        <v>3</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="J9" s="1">
+        <v>50</v>
+      </c>
+      <c r="K9" s="1">
+        <v>200</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
         <v>1</v>
       </c>
-      <c r="H9" s="1">
-        <v>3</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J9" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="K9" s="1">
-        <v>50</v>
-      </c>
-      <c r="L9" s="1">
-        <v>200</v>
-      </c>
-      <c r="M9" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="N9" s="1">
-        <v>0</v>
-      </c>
-      <c r="O9" s="1">
-        <v>1</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>44</v>
+      <c r="O9" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:16">
+    <row r="10" ht="15" customHeight="1" spans="1:15">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>102</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
@@ -1579,44 +1547,41 @@
         <v>2</v>
       </c>
       <c r="G10" s="1">
+        <v>5</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1">
+        <v>200</v>
+      </c>
+      <c r="K10" s="1">
+        <v>500</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
         <v>2</v>
       </c>
-      <c r="H10" s="1">
-        <v>5</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10" s="1">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1">
-        <v>200</v>
-      </c>
-      <c r="L10" s="1">
-        <v>500</v>
-      </c>
-      <c r="M10" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="N10" s="1">
-        <v>0</v>
-      </c>
-      <c r="O10" s="1">
-        <v>2</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>46</v>
+      <c r="O10" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:16">
+    <row r="11" ht="15" customHeight="1" spans="1:15">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>103</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
@@ -1625,34 +1590,31 @@
         <v>3</v>
       </c>
       <c r="G11" s="1">
+        <v>8</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="J11" s="1">
+        <v>500</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1500</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1">
         <v>3</v>
       </c>
-      <c r="H11" s="1">
-        <v>8</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J11" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="K11" s="1">
-        <v>500</v>
-      </c>
-      <c r="L11" s="1">
-        <v>1500</v>
-      </c>
-      <c r="M11" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="N11" s="1">
-        <v>1</v>
-      </c>
-      <c r="O11" s="1">
-        <v>3</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>49</v>
+      <c r="O11" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/TreasureBoxTable.xlsx
+++ b/AAAGameData/DataTables/TreasureBoxTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="53">
   <si>
     <t>#</t>
   </si>
@@ -128,49 +128,64 @@
     <t>破损的宝箱</t>
   </si>
   <si>
-    <t>1:10</t>
-  </si>
-  <si>
-    <t>一个看起来很可疑的箱子</t>
+    <t>1:50,18:30,20:40,21:30,6:10,26:5</t>
+  </si>
+  <si>
+    <t>一个看起来很可疑的箱子，主要包含初级物资和低品质物品</t>
   </si>
   <si>
     <t>精致的宝箱</t>
   </si>
   <si>
-    <t>华丽的宝箱，散发着神秘光芒</t>
+    <t>1:20,18:20,21:30,22:40,10:25,6:15,7:10</t>
+  </si>
+  <si>
+    <t>华丽的宝箱，散发着神秘光芒，包含中等品质物品</t>
   </si>
   <si>
     <t>华丽的宝箱</t>
   </si>
   <si>
-    <t>满是珍宝的宝箱</t>
+    <t>2:30,10:35,22:30,23:25,11:20,7:15,16:10</t>
+  </si>
+  <si>
+    <t>满是珍宝的宝箱，包含高品质装备和稀有卡牌</t>
   </si>
   <si>
     <t>神秘的宝箱</t>
   </si>
   <si>
-    <t>传说中的古董宝藏</t>
+    <t>3:25,11:30,23:35,24:40,15:35,17:30,8:20,27:10,28:10,29:10</t>
+  </si>
+  <si>
+    <t>传说中的古董宝藏，包含顶级装备和传奇宝物</t>
   </si>
   <si>
     <t>普通敌人奖励</t>
   </si>
   <si>
-    <t>普通敌人战斗奖励</t>
+    <t>1:60,18:40,20:30,21:20,6:15,17:5,9:3</t>
+  </si>
+  <si>
+    <t>普通敌人战斗奖励，主要掉落消耗品和低品质卡牌，小概率掉落宝物</t>
   </si>
   <si>
     <t>精英敌人奖励</t>
   </si>
   <si>
-    <t>精英敌人战斗奖励</t>
+    <t>2:30,10:35,16:25,22:30,7:25,19:15,17:15,15:8,5:10</t>
+  </si>
+  <si>
+    <t>精英敌人战斗奖励，掉落中高品质装备和卡牌，有一定概率掉落宝物</t>
   </si>
   <si>
     <t>Boss奖励</t>
   </si>
   <si>
-    <t>1:10,9:-1</t>
-  </si>
-  <si>
-    <t>Boss战斗奖励</t>
+    <t>3:20,11:25,15:50,17:60,23:20,24:35,8:25,4:30,27:15,28:15,29:15,30:25</t>
+  </si>
+  <si>
+    <t>Boss战斗奖励，必定掉落宝物，还有稀有装备和顶级卡牌</t>
   </si>
 </sst>
 </file>
@@ -1143,19 +1158,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
     <col min="6" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="47" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="24" customWidth="1"/>
     <col min="13" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="28" customWidth="1"/>
+    <col min="15" max="15" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -1329,10 +1344,10 @@
         <v>2501</v>
       </c>
       <c r="F5" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>33</v>
@@ -1378,7 +1393,7 @@
         <v>6</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I6" s="1">
         <v>0.6</v>
@@ -1399,7 +1414,7 @@
         <v>3</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:15">
@@ -1409,19 +1424,19 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7" s="1">
         <v>2503</v>
       </c>
       <c r="F7" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="I7" s="1">
         <v>0.8</v>
@@ -1442,7 +1457,7 @@
         <v>4</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:15">
@@ -1452,19 +1467,19 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E8" s="1">
         <v>2504</v>
       </c>
       <c r="F8" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
         <v>10</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
@@ -1485,7 +1500,7 @@
         <v>5</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:15">
@@ -1495,7 +1510,7 @@
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -1507,7 +1522,7 @@
         <v>3</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="I9" s="1">
         <v>0.4</v>
@@ -1528,7 +1543,7 @@
         <v>1</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:15">
@@ -1538,7 +1553,7 @@
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
@@ -1550,7 +1565,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="I10" s="1">
         <v>1</v>
@@ -1571,7 +1586,7 @@
         <v>2</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:15">
@@ -1581,7 +1596,7 @@
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
@@ -1593,7 +1608,7 @@
         <v>8</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="I11" s="1">
         <v>0.8</v>
@@ -1614,7 +1629,7 @@
         <v>3</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
